--- a/reports/集团总公司_现金流量表_2026-11.xlsx
+++ b/reports/集团总公司_现金流量表_2026-11.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>194824500</v>
+        <v>190750434</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>2205670428</v>
+        <v>2166503127</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3897377</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>44647877</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1943251</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>22296067</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>971267</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>11163567</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>779733</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>8918448</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>581149</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>6697155</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>390686</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4460462</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>290215</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3347312</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>195387</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2231212</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>484080</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>5576312</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>245061</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2804503</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>154300</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1772365</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>529523</v>
+        <v>519969</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>6075867</v>
+        <v>5969847</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3596760</v>
+        <v>3540975</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>41270040</v>
+        <v>40540046</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>198950783</v>
+        <v>204743884</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>119892000</v>
+        <v>117303313</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1375668000</v>
+        <v>1352137005</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1301332</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>14879125</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>969640</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>11149805</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>648917</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>7441892</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>486328</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>5573841</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>323428</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3721129</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>245125</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2801486</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24178220</v>
+        <v>23617782</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>277426380</v>
+        <v>272309995</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11189920</v>
+        <v>11040221</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>128395680</v>
+        <v>126025054</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5095410</v>
+        <v>4974630</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>58465890</v>
+        <v>57366246</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>160355550</v>
+        <v>160910716</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>38595233</v>
+        <v>43833168</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>242092</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2719200</v>
+        <v>2674587</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2113413</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>23793000</v>
+        <v>23368802</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1301279</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>14502400</v>
+        <v>14245455</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2355505</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20243016</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>226600000</v>
+        <v>222084837</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2918990</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>32857000</v>
+        <v>32143762</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14336791</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>160886000</v>
+        <v>157798580</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>523485</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>5891600</v>
+        <v>5788050</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20766501</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18410996</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4747190</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>53251000</v>
+        <v>52332254</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7593078</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>84975000</v>
+        <v>83428719</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7575014</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>84975000</v>
+        <v>83550482</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>243811</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2719200</v>
+        <v>2671291</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12584079</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6205316</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>69113000</v>
+        <v>67905714</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6144403</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>69113000</v>
+        <v>67928475</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1016536</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>11330000</v>
+        <v>11134078</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>882463</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>9857100</v>
+        <v>9691134</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>126414</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1416250</v>
+        <v>1390530</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7348266</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5235813</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>25241283</v>
+        <v>30657985</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>25241283</v>
+        <v>30657985</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
